--- a/ci-cd-merge-resolver/repoCollector/datasets/OpenPDF.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/OpenPDF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,15 @@
   </si>
   <si>
     <t>dc154e5dd754dd70cc9100c01cbad7df3b19f6ff</t>
+  </si>
+  <si>
+    <t>1e3019199449215f1d844bdf011424e3241b7a28</t>
+  </si>
+  <si>
+    <t>c256a30ea44e442017202faf49dcacb87becf745</t>
+  </si>
+  <si>
+    <t>5acba6edeac110e35a1959699a9e1dcc1325a9f8</t>
   </si>
 </sst>
 </file>
@@ -95,7 +104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -150,15 +159,47 @@
         <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1.8569999933242798</v>
+        <v>1.1640000343322754</v>
       </c>
       <c r="J2" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>0.8469999432563782</v>
+      </c>
+      <c r="J3" t="b" s="0">
         <v>0</v>
       </c>
     </row>
